--- a/webapp/public/templates/11. THIẾT BỊ PHỤ TRỢ_QUÝ.xlsx
+++ b/webapp/public/templates/11. THIẾT BỊ PHỤ TRỢ_QUÝ.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B7_QUÝ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,58 +413,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Cột 1</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Cột 2</t>
+          <t>Trung tâm viễn thông</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Cột 3</t>
+          <t>Số CSHT</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Cột 4</t>
+          <t>Số CSHT</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Cột 5</t>
+          <t>Máy nổ</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cột 6</t>
+          <t>Máy nổ</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Cột 7</t>
+          <t>Máy lạnh</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Cột 8</t>
+          <t>Máy lạnh</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Cột 9</t>
+          <t>Accu</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Cột 10</t>
+          <t>Accu</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Tủ nguồn</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Tủ nguồn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Tổng thiết bị</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Tổng thiết bị</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Đức Hòa</t>
         </is>
       </c>
     </row>

--- a/webapp/public/templates/11. THIẾT BỊ PHỤ TRỢ_QUÝ.xlsx
+++ b/webapp/public/templates/11. THIẾT BỊ PHỤ TRỢ_QUÝ.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,14 +491,1661 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bến Lức</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bến Cầu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>301</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bến Lức</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cần Đước</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cần Giuộc</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Châu Thành</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Đức Hòa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Đức Huệ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dương Minh Châu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gò Dầu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hòa Thành</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kiến Tường</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Long An</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tầm Vu</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tân Biên</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tân Châu</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tân Ninh</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tân Thạnh</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tân Trụ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Thạnh Hóa</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Thủ Thừa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Trảng Bàng</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Vĩnh Hưng</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1,737</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1,737</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1,106</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1,106</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2,350</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2,350</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1,911</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1,911</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1,654</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1,654</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>7,021</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>7,021</t>
         </is>
       </c>
     </row>
